--- a/artfynd/A 60865-2025 artfynd.xlsx
+++ b/artfynd/A 60865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109759426</v>
+        <v>105237263</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredemad, Sm</t>
+          <t>Bredemads avfallsanläggning, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434507.9938259476</v>
+        <v>434883</v>
       </c>
       <c r="R2" t="n">
-        <v>6303436.923263695</v>
+        <v>6302624</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På låga. JMN0090 (Calluna AB) Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +765,371 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104976230</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bredemads avfallsanläggning, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>434607</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6303403</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kretsande på hög höjd. Släpps för att följa BG JPN0005 (Calluna AB) rovfågelinventering.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109759426</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bredemad, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>434508</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6303437</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Krister Wahlström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Krister Wahlström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104976243</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103060</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brun glada</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Milvus migrans</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bredemads avfallsanläggning, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>434632</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6303396</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>JPN0005 (Calluna AB) rovfågelinventering.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60865-2025 artfynd.xlsx
+++ b/artfynd/A 60865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105237263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104976230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109759426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,8 +1150,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104976243</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>